--- a/backend/data/users.xlsx
+++ b/backend/data/users.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,21 @@
   </si>
   <si>
     <t>free</t>
+  </si>
+  <si>
+    <t>a8e777aa-b372-451a-bd64-ac716e5daaf5</t>
+  </si>
+  <si>
+    <t>kishans</t>
+  </si>
+  <si>
+    <t>kishanmihani918@gmail.coms</t>
+  </si>
+  <si>
+    <t>Kishan@1234</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -439,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="8" width="20" customWidth="1"/>
@@ -520,6 +535,29 @@
         <v>46019.24138951389</v>
       </c>
     </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46034.77233337963</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
